--- a/petz-automation/src/test/resources/testdata/login-data.xlsx
+++ b/petz-automation/src/test/resources/testdata/login-data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
   <si>
     <t>caseId</t>
   </si>
@@ -22,9 +22,6 @@
     <t>field</t>
   </si>
   <si>
-    <t>dimension</t>
-  </si>
-  <si>
     <t>value</t>
   </si>
   <si>
@@ -43,9 +40,6 @@
     <t>email</t>
   </si>
   <si>
-    <t>BVA</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -73,45 +67,6 @@
     <t>aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa@example.com</t>
   </si>
   <si>
-    <t>EMAIL_EP_INVALID</t>
-  </si>
-  <si>
-    <t>EP</t>
-  </si>
-  <si>
-    <t>abcxyz</t>
-  </si>
-  <si>
-    <t>Email format invalid</t>
-  </si>
-  <si>
-    <t>EMAIL_EP_VALID</t>
-  </si>
-  <si>
-    <t>valid.user@petz.com</t>
-  </si>
-  <si>
-    <t>EMAIL_MONKEY_SQLI</t>
-  </si>
-  <si>
-    <t>MONKEY</t>
-  </si>
-  <si>
-    <t>' OR '1'='1</t>
-  </si>
-  <si>
-    <t>EMAIL_MONKEY_XSS</t>
-  </si>
-  <si>
-    <t>&lt;script&gt;alert('xss')&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>EMAIL_MONKEY_UNICODE</t>
-  </si>
-  <si>
-    <t>用户@petz.com</t>
-  </si>
-  <si>
     <t>PWD_BVA_EMPTY</t>
   </si>
   <si>
@@ -125,15 +80,6 @@
   </si>
   <si>
     <t>a</t>
-  </si>
-  <si>
-    <t>PWD_EP_VALID</t>
-  </si>
-  <si>
-    <t>Admin@petz123</t>
-  </si>
-  <si>
-    <t>PWD_MONKEY_SQLI</t>
   </si>
   <si>
     <t>role</t>
@@ -265,16 +211,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.8046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.94140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="8.62890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.5390625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="70.17578125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.5390625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="18.37890625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.6328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="70.17578125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.5390625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="18.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="17.6328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -296,284 +241,105 @@
       <c r="F1" t="s" s="1">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="1">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>8</v>
-      </c>
       <c r="C2" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="F2" t="s" s="0">
         <v>11</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>11</v>
-      </c>
       <c r="F3" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D4" t="s" s="0">
-        <v>18</v>
-      </c>
       <c r="E4" t="s" s="0">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s" s="0">
         <v>19</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G13" t="s" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -599,79 +365,79 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s" s="2">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s" s="2">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s" s="2">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -695,55 +461,55 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
